--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134656422</v>
+        <v>135153562</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>106437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>674</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Myskmåra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Galium triflorum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -743,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,6 +774,107 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134656422</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -876,6 +876,112 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135219611</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bredänget, Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>850687</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7369965</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,57 +878,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135219611</v>
+        <v>135255652</v>
       </c>
       <c r="B4" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bredänget, Bredänget, Nb</t>
+          <t>Svartbyn, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>850687</v>
+        <v>850655</v>
       </c>
       <c r="R4" t="n">
-        <v>7369965</v>
+        <v>7369866</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,12 +951,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,15 +986,837 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135255653</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>850645</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7369886</v>
+      </c>
+      <c r="S5" t="n">
+        <v>11</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135255654</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>850661</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7369964</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135255655</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>850653</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7369969</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på björk</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135255656</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>850656</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7369989</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på björk</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135255657</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>850653</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7370002</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135255658</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>850651</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7370010</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135219611</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bredänget, Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>850687</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7369965</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1714,54 +1714,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135219611</v>
+        <v>135316983</v>
       </c>
       <c r="B11" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bredänget, Bredänget, Nb</t>
+          <t>Tretåig Hackspett, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>850687</v>
+        <v>850659</v>
       </c>
       <c r="R11" t="n">
-        <v>7369965</v>
+        <v>7369886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,12 +1783,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,15 +1803,325 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135219611</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bredänget, Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>850687</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7369965</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135317367</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135317389</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Knärot, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>850670</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7369968</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135153562</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134656422</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255652</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255653</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255654</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1354,6 +1384,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255655</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1473,6 +1508,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255656</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,6 +1632,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255657</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1711,6 +1756,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255658</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135316983</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1918,6 +1973,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135219611</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2020,6 +2080,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135317367</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2122,8 +2187,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135317389</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135153562</v>
       </c>
       <c r="B2" t="n">
-        <v>106437</v>
+        <v>106492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>135255652</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>135255653</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>135255654</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>135255655</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>135255656</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>135255657</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>135255658</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>135316983</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,54 +1870,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135219611</v>
+        <v>135605668</v>
       </c>
       <c r="B12" t="n">
-        <v>99195</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bredänget, Bredänget, Nb</t>
+          <t>Västra Svartbyn, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>850687</v>
+        <v>850658</v>
       </c>
       <c r="R12" t="n">
-        <v>7369965</v>
+        <v>7370037</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1944,12 +1939,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,27 +1964,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135219611</t>
+          <t>https://artportalen.se/Sighting/135605668</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135317367</v>
+        <v>135219611</v>
       </c>
       <c r="B13" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,24 +2009,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>850736</v>
+        <v>850687</v>
       </c>
       <c r="R13" t="n">
-        <v>7369939</v>
+        <v>7369965</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2064,34 +2069,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135317367</t>
+          <t>https://artportalen.se/Sighting/135219611</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135317389</v>
+        <v>135317367</v>
       </c>
       <c r="B14" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2123,17 +2127,17 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Knärot, Nb</t>
+          <t>BrunBjörn, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>850670</v>
+        <v>850736</v>
       </c>
       <c r="R14" t="n">
-        <v>7369968</v>
+        <v>7369939</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,12 +2161,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,7 +2193,221 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135317367</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135317389</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Knärot, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>850670</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7369968</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135317389</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135605684</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>850739</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7370043</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605684</t>
         </is>
       </c>
     </row>
@@ -2208,6 +2426,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135153562</v>
       </c>
       <c r="B2" t="n">
-        <v>106492</v>
+        <v>106519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>135219611</v>
       </c>
       <c r="B13" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>135317367</v>
       </c>
       <c r="B14" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>135317389</v>
       </c>
       <c r="B15" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>135605684</v>
       </c>
       <c r="B16" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2408,6 +2408,118 @@
       <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135605684</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135718208</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>850717</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7370051</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Brjan Xotta</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Brjan Xotta</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135718208</t>
         </is>
       </c>
     </row>
@@ -2428,6 +2540,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,51 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134656422</v>
+        <v>135819545</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>92273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>850736</v>
+        <v>850682</v>
       </c>
       <c r="R3" t="n">
-        <v>7369939</v>
+        <v>7370041</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,25 +866,2638 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135819545</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134656422</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134656422</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135645133</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79465</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åkerbär, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>850648</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7369924</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645133</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135665676</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78799</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tretåig Hackspett, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>850659</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7369886</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135665676</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135255652</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>850655</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7369866</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255652</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135255653</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>850645</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7369886</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255653</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135255654</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>850661</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7369964</v>
+      </c>
+      <c r="S9" t="n">
+        <v>16</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255654</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135255655</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>850653</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7369969</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på björk</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255655</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135255656</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>850656</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7369989</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på björk</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255656</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135255657</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>850653</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7370002</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255657</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135255658</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>850651</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7370010</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255658</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135316983</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tretåig Hackspett, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>850659</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7369886</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135316983</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135605668</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västra Svartbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>850658</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7370037</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605668</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135664971</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Spilling</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135664971</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135798223</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57158</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spilling</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135798223</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135819444</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bredänget, Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>850692</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7370029</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819444</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135819354</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bredänget, Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>850709</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7370035</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135819354</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135219611</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bredänget, Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>850687</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7369965</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135219611</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135317367</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S21" t="n">
+        <v>100</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135317367</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135317389</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Knärot, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>850670</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7369968</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135317389</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135605684</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>850739</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7370043</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135605684</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135718208</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bredänget, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>850717</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7370051</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Brjan Xotta</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Brjan Xotta</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135718208</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135664430</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99551</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S25" t="n">
+        <v>100</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135664430</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135664877</v>
+      </c>
+      <c r="B26" t="n">
+        <v>103990</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S26" t="n">
+        <v>100</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135664877</t>
         </is>
       </c>
     </row>
@@ -895,6 +3505,29 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135819545</v>
       </c>
       <c r="B3" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>135219611</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>135317367</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>135317389</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>135605684</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135718208</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>135664430</v>
       </c>
       <c r="B25" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>135664877</v>
       </c>
       <c r="B26" t="n">
-        <v>103990</v>
+        <v>103992</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2196,52 +2196,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135605668</v>
+        <v>135664971</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57167</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Svartbyn, Nb</t>
+          <t>BrunBjörn, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>850658</v>
+        <v>850736</v>
       </c>
       <c r="R15" t="n">
-        <v>7370037</v>
+        <v>7369939</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2265,17 +2261,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Spilling</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,16 +2307,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605668</t>
+          <t>https://artportalen.se/Sighting/135664971</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135664971</v>
+        <v>135798223</v>
       </c>
       <c r="B16" t="n">
-        <v>57167</v>
+        <v>57158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,21 +2324,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2372,22 +2378,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2418,16 +2414,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135664971</t>
+          <t>https://artportalen.se/Sighting/135798223</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135798223</v>
+        <v>135819444</v>
       </c>
       <c r="B17" t="n">
-        <v>57158</v>
+        <v>5201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,16 +2431,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2455,17 +2451,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>850736</v>
+        <v>850692</v>
       </c>
       <c r="R17" t="n">
-        <v>7369939</v>
+        <v>7370029</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,17 +2485,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spilling</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,27 +2505,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135798223</t>
+          <t>https://artportalen.se/Sighting/135819444</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135819444</v>
+        <v>135819354</v>
       </c>
       <c r="B18" t="n">
-        <v>5201</v>
+        <v>8450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2542,21 +2533,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2566,10 +2557,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>850692</v>
+        <v>850709</v>
       </c>
       <c r="R18" t="n">
-        <v>7370029</v>
+        <v>7370035</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2627,54 +2618,63 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819444</t>
+          <t>https://artportalen.se/Sighting/135819354</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135819354</v>
+        <v>135219611</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>850709</v>
+        <v>850687</v>
       </c>
       <c r="R19" t="n">
-        <v>7370035</v>
+        <v>7369965</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,24 +2718,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819354</t>
+          <t>https://artportalen.se/Sighting/135219611</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135219611</v>
+        <v>135317367</v>
       </c>
       <c r="B20" t="n">
         <v>99276</v>
@@ -2763,29 +2763,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bredänget, Bredänget, Nb</t>
+          <t>BrunBjörn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>850687</v>
+        <v>850736</v>
       </c>
       <c r="R20" t="n">
-        <v>7369965</v>
+        <v>7369939</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2823,30 +2818,31 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135219611</t>
+          <t>https://artportalen.se/Sighting/135317367</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135317367</v>
+        <v>135317389</v>
       </c>
       <c r="B21" t="n">
         <v>99276</v>
@@ -2881,17 +2877,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Knärot, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>850736</v>
+        <v>850670</v>
       </c>
       <c r="R21" t="n">
-        <v>7369939</v>
+        <v>7369968</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2915,12 +2911,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,13 +2943,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135317367</t>
+          <t>https://artportalen.se/Sighting/135317389</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135317389</v>
+        <v>135718208</v>
       </c>
       <c r="B22" t="n">
         <v>99276</v>
@@ -2982,20 +2978,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Knärot, Nb</t>
+          <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>850670</v>
+        <v>850717</v>
       </c>
       <c r="R22" t="n">
-        <v>7369968</v>
+        <v>7370051</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3022,12 +3014,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,76 +3038,71 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Brjan Xotta</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Brjan Xotta</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135317389</t>
+          <t>https://artportalen.se/Sighting/135718208</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135605684</v>
+        <v>135664430</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>222812</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>BrunBjörn, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>850739</v>
+        <v>850736</v>
       </c>
       <c r="R23" t="n">
-        <v>7370043</v>
+        <v>7369939</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3129,12 +3126,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3143,7 +3150,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3161,54 +3167,54 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135605684</t>
+          <t>https://artportalen.se/Sighting/135664430</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135718208</v>
+        <v>135664877</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>103992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>223284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>BrunBjörn, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>850717</v>
+        <v>850736</v>
       </c>
       <c r="R24" t="n">
-        <v>7370051</v>
+        <v>7369939</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3232,22 +3238,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,240 +3268,16 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Brjan Xotta</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Brjan Xotta</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135718208</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>135664430</v>
-      </c>
-      <c r="B25" t="n">
-        <v>99553</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>222812</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Liljekonvalj</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Convallaria majalis</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>BrunBjörn, Nb</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>850736</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7369939</v>
-      </c>
-      <c r="S25" t="n">
-        <v>100</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Linnea  Isaksson</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Linnea  Isaksson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135664430</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>135664877</v>
-      </c>
-      <c r="B26" t="n">
-        <v>103992</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>223284</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>BrunBjörn, Nb</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>850736</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7369939</v>
-      </c>
-      <c r="S26" t="n">
-        <v>100</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Överkalix</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Linnea  Isaksson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Linnea  Isaksson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135664877</t>
         </is>
@@ -3526,8 +3308,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23383-2026 artfynd.xlsx
+++ b/artfynd/A 23383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2196,48 +2196,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135664971</v>
+        <v>135605668</v>
       </c>
       <c r="B15" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Västra Svartbyn, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>850736</v>
+        <v>850658</v>
       </c>
       <c r="R15" t="n">
-        <v>7369939</v>
+        <v>7370037</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2261,27 +2265,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spilling</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,16 +2301,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135664971</t>
+          <t>https://artportalen.se/Sighting/135605668</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135798223</v>
+        <v>135664971</v>
       </c>
       <c r="B16" t="n">
-        <v>57158</v>
+        <v>57167</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,21 +2318,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2378,12 +2372,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2414,16 +2418,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135798223</t>
+          <t>https://artportalen.se/Sighting/135664971</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135819444</v>
+        <v>135798223</v>
       </c>
       <c r="B17" t="n">
-        <v>5201</v>
+        <v>57158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,16 +2435,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2451,17 +2455,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bredänget, Bredänget, Nb</t>
+          <t>BrunBjörn, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>850692</v>
+        <v>850736</v>
       </c>
       <c r="R17" t="n">
-        <v>7370029</v>
+        <v>7369939</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2485,12 +2489,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spilling</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,27 +2514,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819444</t>
+          <t>https://artportalen.se/Sighting/135798223</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135819354</v>
+        <v>135819444</v>
       </c>
       <c r="B18" t="n">
-        <v>8450</v>
+        <v>5201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2533,21 +2542,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2557,10 +2566,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>850709</v>
+        <v>850692</v>
       </c>
       <c r="R18" t="n">
-        <v>7370035</v>
+        <v>7370029</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2618,63 +2627,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819354</t>
+          <t>https://artportalen.se/Sighting/135819444</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135219611</v>
+        <v>135819354</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>850687</v>
+        <v>850709</v>
       </c>
       <c r="R19" t="n">
-        <v>7369965</v>
+        <v>7370035</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,24 +2718,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135219611</t>
+          <t>https://artportalen.se/Sighting/135819354</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135317367</v>
+        <v>135219611</v>
       </c>
       <c r="B20" t="n">
         <v>99276</v>
@@ -2763,24 +2763,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Bredänget, Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>850736</v>
+        <v>850687</v>
       </c>
       <c r="R20" t="n">
-        <v>7369939</v>
+        <v>7369965</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2818,31 +2823,30 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135317367</t>
+          <t>https://artportalen.se/Sighting/135219611</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135317389</v>
+        <v>135317367</v>
       </c>
       <c r="B21" t="n">
         <v>99276</v>
@@ -2877,17 +2881,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Knärot, Nb</t>
+          <t>BrunBjörn, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>850670</v>
+        <v>850736</v>
       </c>
       <c r="R21" t="n">
-        <v>7369968</v>
+        <v>7369939</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2911,12 +2915,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2943,13 +2947,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135317389</t>
+          <t>https://artportalen.se/Sighting/135317367</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135718208</v>
+        <v>135317389</v>
       </c>
       <c r="B22" t="n">
         <v>99276</v>
@@ -2978,16 +2982,20 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bredänget, Nb</t>
+          <t>Knärot, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>850717</v>
+        <v>850670</v>
       </c>
       <c r="R22" t="n">
-        <v>7370051</v>
+        <v>7369968</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3014,22 +3022,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3038,71 +3036,76 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Brjan Xotta</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Brjan Xotta</t>
+          <t>Linnea  Isaksson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135718208</t>
+          <t>https://artportalen.se/Sighting/135317389</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135664430</v>
+        <v>135605684</v>
       </c>
       <c r="B23" t="n">
-        <v>99553</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222812</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>850736</v>
+        <v>850739</v>
       </c>
       <c r="R23" t="n">
-        <v>7369939</v>
+        <v>7370043</v>
       </c>
       <c r="S23" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3126,22 +3129,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,6 +3143,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3167,54 +3161,54 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135664430</t>
+          <t>https://artportalen.se/Sighting/135605684</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135664877</v>
+        <v>135718208</v>
       </c>
       <c r="B24" t="n">
-        <v>103992</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>223284</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BrunBjörn, Nb</t>
+          <t>Bredänget, Nb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>850736</v>
+        <v>850717</v>
       </c>
       <c r="R24" t="n">
-        <v>7369939</v>
+        <v>7370051</v>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3238,22 +3232,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3268,16 +3262,240 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Brjan Xotta</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea  Isaksson</t>
+          <t>Brjan Xotta</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135718208</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135664430</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99553</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S25" t="n">
+        <v>100</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135664430</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135664877</v>
+      </c>
+      <c r="B26" t="n">
+        <v>103992</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>BrunBjörn, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>850736</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7369939</v>
+      </c>
+      <c r="S26" t="n">
+        <v>100</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linnea  Isaksson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135664877</t>
         </is>
@@ -3308,6 +3526,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
